--- a/FLORES DE ESTRADA/Septiembre/RESUMEN-Septiembre-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Septiembre/RESUMEN-Septiembre-ESTRADA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\FLORES DE ESTRADA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7615E75E-61E4-4D29-A8DF-2A0AA032289D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9612EC0D-6315-433F-B68A-610458AB4B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Egresos gastos del mes - SEPTIEMBRE EXTRAORDINARIO</t>
+  </si>
+  <si>
+    <t>Alterini Guido -Jardineria</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -545,15 +548,13 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -892,15 +893,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="24"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -910,7 +911,7 @@
       <c r="G1" s="25"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -924,7 +925,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -938,7 +939,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -952,7 +953,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -964,7 +965,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -974,7 +975,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
@@ -988,7 +989,7 @@
       <c r="G7" s="31"/>
       <c r="H7" s="32"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -998,7 +999,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="26"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>6</v>
       </c>
@@ -1012,7 +1013,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1027,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1036,7 +1037,7 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
         <v>15</v>
       </c>
@@ -1048,7 +1049,7 @@
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
         <v>34</v>
       </c>
@@ -1058,11 +1059,11 @@
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
-      <c r="H13" s="64">
+      <c r="H13" s="37">
         <v>218000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57"/>
       <c r="B14" s="57"/>
       <c r="C14" s="57"/>
@@ -1072,7 +1073,7 @@
       <c r="G14" s="57"/>
       <c r="H14" s="37"/>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>9</v>
       </c>
@@ -1087,7 +1088,7 @@
         <v>218000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
         <v>10</v>
       </c>
@@ -1099,7 +1100,7 @@
       <c r="G16" s="56"/>
       <c r="H16" s="56"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
         <v>39</v>
       </c>
@@ -1109,11 +1110,11 @@
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
       <c r="G17" s="36"/>
-      <c r="H17" s="60">
+      <c r="H17" s="43">
         <v>29691.4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>11</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>29691.4</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="56" t="s">
         <v>19</v>
       </c>
@@ -1140,7 +1141,7 @@
       <c r="G19" s="56"/>
       <c r="H19" s="56"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>20</v>
       </c>
@@ -1154,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>30</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
         <v>9</v>
       </c>
@@ -1183,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="56" t="s">
         <v>21</v>
       </c>
@@ -1195,7 +1196,7 @@
       <c r="G23" s="56"/>
       <c r="H23" s="56"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>40</v>
       </c>
@@ -1205,23 +1206,25 @@
       <c r="E24" s="58"/>
       <c r="F24" s="58"/>
       <c r="G24" s="58"/>
-      <c r="H24" s="60">
+      <c r="H24" s="43">
         <v>70000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="62"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="61">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="43">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
         <v>37</v>
       </c>
@@ -1231,11 +1234,11 @@
       <c r="E26" s="45"/>
       <c r="F26" s="45"/>
       <c r="G26" s="45"/>
-      <c r="H26" s="60">
+      <c r="H26" s="43">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="50" t="s">
         <v>36</v>
       </c>
@@ -1245,11 +1248,11 @@
       <c r="E27" s="45"/>
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
-      <c r="H27" s="60">
+      <c r="H27" s="43">
         <v>125200</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
         <v>12</v>
       </c>
@@ -1261,10 +1264,10 @@
       <c r="G28" s="38"/>
       <c r="H28" s="40">
         <f>SUM(H24:H27)</f>
-        <v>440200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>280200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="56" t="s">
         <v>22</v>
       </c>
@@ -1276,7 +1279,7 @@
       <c r="G29" s="56"/>
       <c r="H29" s="56"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
         <v>13</v>
       </c>
@@ -1293,7 +1296,7 @@
       <c r="H30" s="36"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
         <v>41</v>
       </c>
@@ -1311,7 +1314,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="56" t="s">
         <v>23</v>
       </c>
@@ -1323,7 +1326,7 @@
       <c r="G32" s="56"/>
       <c r="H32" s="56"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="36" t="s">
         <v>27</v>
       </c>
@@ -1333,11 +1336,11 @@
       <c r="E33" s="36"/>
       <c r="F33" s="36"/>
       <c r="G33" s="36"/>
-      <c r="H33" s="49">
+      <c r="H33" s="62">
         <v>99656</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="47" t="s">
         <v>24</v>
       </c>
@@ -1349,10 +1352,10 @@
       <c r="G34" s="47"/>
       <c r="H34" s="48">
         <f>H33+H31+H28+H22+H18+H15</f>
-        <v>935647.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>775647.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
         <v>32</v>
       </c>
@@ -1363,13 +1366,13 @@
       <c r="F35" s="34"/>
       <c r="G35" s="34"/>
       <c r="H35" s="35">
-        <f>1302201-851600</f>
-        <v>450601</v>
+        <f>1400000-775647.4</f>
+        <v>624352.6</v>
       </c>
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
     </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
         <v>29</v>
       </c>
@@ -1381,11 +1384,11 @@
       <c r="G36" s="34"/>
       <c r="H36" s="35">
         <f>H34+H35</f>
-        <v>1386248.4</v>
+        <v>1400000</v>
       </c>
       <c r="I36" s="23"/>
     </row>
-    <row r="37" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="59" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
@@ -1398,7 +1401,7 @@
       <c r="G37" s="59"/>
       <c r="H37" s="33"/>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="52" t="s">
         <v>16</v>
       </c>
@@ -1410,7 +1413,7 @@
       <c r="G38" s="52"/>
       <c r="H38" s="52"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="52"/>
       <c r="B39" s="52"/>
       <c r="C39" s="52"/>
@@ -1420,7 +1423,7 @@
       <c r="G39" s="52"/>
       <c r="H39" s="52"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -1430,7 +1433,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="53"/>
       <c r="B41" s="54"/>
       <c r="C41" s="54"/>
@@ -1441,7 +1444,7 @@
       <c r="H41" s="55"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>18</v>
       </c>
@@ -1452,10 +1455,10 @@
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
       <c r="H42" s="16">
-        <v>3443521.1724729966</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>4128514.453567781</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>31</v>
       </c>
@@ -1466,10 +1469,10 @@
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
       <c r="H43" s="18">
-        <v>1554639.1810947841</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>2432930.8005127362</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>28</v>
       </c>
@@ -1480,12 +1483,11 @@
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
       <c r="H44" s="49">
-        <f>-12057-5988.47</f>
-        <v>-18045.47</v>
+        <v>0</v>
       </c>
       <c r="I44" s="19"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>42</v>
       </c>
@@ -1497,10 +1499,10 @@
       <c r="G45" s="12"/>
       <c r="H45" s="13">
         <f>-( H34 )</f>
-        <v>-935647.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>-775647.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>43</v>
       </c>
@@ -1512,7 +1514,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="13"/>
     </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>17</v>
       </c>
@@ -1524,10 +1526,10 @@
       <c r="G47" s="15"/>
       <c r="H47" s="17">
         <f>SUM(H42:H46)</f>
-        <v>4044467.4835677813</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>5785797.8540805168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -1537,7 +1539,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
       <c r="B49" s="51" t="s">
         <v>33</v>
@@ -1549,7 +1551,7 @@
       <c r="G49" s="51"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
       <c r="B50" s="51"/>
       <c r="C50" s="51"/>
@@ -1559,7 +1561,7 @@
       <c r="G50" s="51"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
       <c r="B51" s="51"/>
       <c r="C51" s="51"/>
@@ -1569,7 +1571,7 @@
       <c r="G51" s="51"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
       <c r="B52" s="51"/>
       <c r="C52" s="51"/>
@@ -1579,7 +1581,7 @@
       <c r="G52" s="51"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
       <c r="B53" s="51"/>
       <c r="C53" s="51"/>
@@ -1589,7 +1591,7 @@
       <c r="G53" s="51"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="51"/>
       <c r="C54" s="51"/>
